--- a/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,100 +439,200 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>00981A_異動類型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>00981A_調整方向</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>00981A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>00981A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>00981A_權重_今日</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>00981A_權重變化</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>00981A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>00981A_股數_今日</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>00981A_股數變化</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>00991A_異動類型</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>00991A_調整方向</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>00991A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>00991A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>00991A_權重_今日</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>00991A_權重變化</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>00991A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>00991A_股數_今日</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>00991A_股數變化</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -541,12 +641,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -554,101 +654,385 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>00981A,00991A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9.87%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9.29%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11884000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11264000</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-620,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>台灣積體</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>台灣積體</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>11.74%</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>11.30%</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-200,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>00407A,00993A</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>宜鼎</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.36%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.36%</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="AF3" t="n">
         <v>65000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="AG3" t="n">
         <v>66294</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>1,294</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>宜鼎國際</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>1.33%</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>1.36%</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>+0.03%</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="AP3" t="n">
         <v>94000</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AQ3" t="n">
         <v>95872</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>1,872</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00407A,00991A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>460000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>380000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-80,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>137000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR4"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,102 +539,52 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00407A_異動類型</t>
+          <t>00403A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00407A_調整方向</t>
+          <t>00403A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_昨日</t>
+          <t>00403A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00407A_股票名稱_今日</t>
+          <t>00403A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00407A_權重_昨日</t>
+          <t>00403A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00407A_權重_今日</t>
+          <t>00403A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00407A_權重變化</t>
+          <t>00403A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00407A_股數_昨日</t>
+          <t>00403A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00407A_股數_今日</t>
+          <t>00403A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00407A_股數變化</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>00993A_異動類型</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>00993A_調整方向</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>00993A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>00993A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>00993A_權重_今日</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>00993A_權重變化</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>00993A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>00993A_股數_今日</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>00993A_股數變化</t>
+          <t>00403A_股數變化</t>
         </is>
       </c>
     </row>
@@ -650,11 +600,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00981A,00991A</t>
+          <t>00403A,00981A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -749,36 +699,62 @@
           <t>-200,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>17.19%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16.02%</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-900,000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -786,19 +762,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>341900</v>
+      </c>
+      <c r="M3" t="n">
+        <v>313900</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -816,223 +828,45 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>65000</v>
+        <v>179500</v>
       </c>
       <c r="AG3" t="n">
-        <v>66294</v>
+        <v>149500</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1,294</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="AP3" t="n">
-        <v>94000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>95872</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>1,872</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>旺矽科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00407A,00991A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>旺矽科技</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>旺矽科技</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2.71%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>460000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>380000</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-80,000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2.89%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2.56%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>157000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>137000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-20,000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+          <t>-30,000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AR4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,52 +539,102 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00403A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00403A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00403A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00403A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00403A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00403A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00403A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00403A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00403A_股數變化</t>
+          <t>00407A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00993A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00993A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00993A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00993A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00993A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00993A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00993A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00993A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00993A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00993A_股數變化</t>
         </is>
       </c>
     </row>
@@ -600,11 +650,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00403A,00981A,00991A</t>
+          <t>00981A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -699,62 +749,36 @@
           <t>-200,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>17.19%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>16.02%</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>-1.17%</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-900,000</t>
-        </is>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -762,55 +786,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00403A,00981A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.80%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>341900</v>
-      </c>
-      <c r="M3" t="n">
-        <v>313900</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>-28,000</t>
-        </is>
-      </c>
+          <t>00407A,00993A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -828,45 +816,223 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>66294</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1,294</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>95872</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1,872</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>00407A,00991A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1.63%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1.39%</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>-0.24%</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>179500</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>149500</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-30,000</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-0.48%</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>460000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>380000</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-80,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2.56%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>137000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR4"/>
+  <dimension ref="A1:BB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,100 +539,150 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>00403A_異動類型</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>00403A_調整方向</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>00403A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00403A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00403A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00403A_權重變化</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00403A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00403A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00403A_股數變化</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>00993A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00993A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00993A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00993A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00993A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00993A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00993A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00993A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00993A_股數變化</t>
         </is>
@@ -650,11 +700,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00981A,00991A</t>
+          <t>00403A,00981A,00991A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -749,16 +799,52 @@
           <t>-200,000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>17.19%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16.02%</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-900,000</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
@@ -769,16 +855,26 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -786,19 +882,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00407A,00993A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>00403A,00981A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>341900</v>
+      </c>
+      <c r="M3" t="n">
+        <v>313900</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -816,101 +948,75 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>65000</v>
+        <v>179500</v>
       </c>
       <c r="AG3" t="n">
-        <v>66294</v>
+        <v>149500</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1,294</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>宜鼎國際</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>1.36%</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="AP3" t="n">
-        <v>94000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>95872</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>1,872</t>
-        </is>
-      </c>
+          <t>-30,000</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>旺矽科技</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -918,7 +1024,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00407A,00991A</t>
+          <t>00407A,00993A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -931,108 +1037,260 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>66294</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>1,294</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>宜鼎國際</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>95872</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1,872</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00407A,00991A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>旺矽科技</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>旺矽科技</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>2.71%</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2.23%</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>-0.48%</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="V5" t="n">
         <v>460000</v>
       </c>
-      <c r="W4" t="n">
+      <c r="W5" t="n">
         <v>380000</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>-80,000</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>旺矽</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>旺矽</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>2.89%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>2.56%</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>-0.33%</t>
         </is>
       </c>
-      <c r="AF4" t="n">
+      <c r="AP5" t="n">
         <v>157000</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AQ5" t="n">
         <v>137000</v>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>-20,000</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
